--- a/artfynd/A 11278-2026 artfynd.xlsx
+++ b/artfynd/A 11278-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131333864</v>
       </c>
       <c r="B2" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>131333481</v>
       </c>
       <c r="B3" t="n">
-        <v>58041</v>
+        <v>58043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11278-2026 artfynd.xlsx
+++ b/artfynd/A 11278-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131333864</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>131333481</v>
       </c>
       <c r="B3" t="n">
-        <v>58043</v>
+        <v>58044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11278-2026 artfynd.xlsx
+++ b/artfynd/A 11278-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131333864</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>131333481</v>
       </c>
       <c r="B3" t="n">
-        <v>58044</v>
+        <v>58045</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11278-2026 artfynd.xlsx
+++ b/artfynd/A 11278-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131333864</v>
       </c>
       <c r="B2" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>131333481</v>
       </c>
       <c r="B3" t="n">
-        <v>58045</v>
+        <v>58048</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11278-2026 artfynd.xlsx
+++ b/artfynd/A 11278-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131333864</v>
       </c>
       <c r="B2" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>131333481</v>
       </c>
       <c r="B3" t="n">
-        <v>58048</v>
+        <v>58049</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11278-2026 artfynd.xlsx
+++ b/artfynd/A 11278-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131333864</v>
       </c>
       <c r="B2" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>131333481</v>
       </c>
       <c r="B3" t="n">
-        <v>58049</v>
+        <v>58055</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11278-2026 artfynd.xlsx
+++ b/artfynd/A 11278-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131333864</v>
       </c>
       <c r="B2" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>131333481</v>
       </c>
       <c r="B3" t="n">
-        <v>58055</v>
+        <v>58056</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11278-2026 artfynd.xlsx
+++ b/artfynd/A 11278-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131333864</v>
       </c>
       <c r="B2" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>131333481</v>
       </c>
       <c r="B3" t="n">
-        <v>58056</v>
+        <v>58059</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11278-2026 artfynd.xlsx
+++ b/artfynd/A 11278-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131333864</v>
       </c>
       <c r="B2" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>131333481</v>
       </c>
       <c r="B3" t="n">
-        <v>58059</v>
+        <v>58061</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11278-2026 artfynd.xlsx
+++ b/artfynd/A 11278-2026 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>131333864</v>
       </c>
       <c r="B2" t="n">
-        <v>57901</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -820,7 +820,7 @@
         <v>131333481</v>
       </c>
       <c r="B3" t="n">
-        <v>58061</v>
+        <v>58112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
